--- a/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">Why!</t>
   </si>
   <si>
-    <t xml:space="preserve">考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+    <t xml:space="preserve">考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
   </si>
   <si>
     <t xml:space="preserve">Think about it. This dragon eats gold, doesn’t it? How are we supposed to feed it when we are hardly wealthy?</t>
@@ -3978,7 +3978,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4101,10 +4101,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -11540,7 +11536,7 @@
       <c r="I686" s="1" t="n">
         <v>411</v>
       </c>
-      <c r="J686" s="31" t="s">
+      <c r="J686" s="7" t="s">
         <v>784</v>
       </c>
       <c r="K686" s="4" t="s">

--- a/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
+++ b/JP (Exclude Game)/Dialog/Drama/loytel.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="871">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -1371,7 +1371,7 @@
 「#pcさん、私たちを見捨てないで…！」</t>
   </si>
   <si>
-    <t xml:space="preserve">...But, I can hear it. The voice of these decayed rocks and withered soil whispering of past glories.
+    <t xml:space="preserve">...But, I can hear it. The voice of these decayed pebbles and withered soil whispering of past glories.
 "#pc, Vernis is not over yet..."
 "#pc, I can still make it..."
 "#pc, don't abandon us...!"</t>
@@ -3809,6 +3809,205 @@
   <si>
     <t xml:space="preserve">key_exile</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">stone_dream</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">stone_dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふぅ、これだけ拠点が大きくなると、帳簿を付けるだけでも一苦労だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whew, now that our settlement has grown this large, keeping the books is becoming quite a task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">だが、こういう地味な仕事ほど、誰かがきちんとやらねばな。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still, it's precisely the sort of mundane work that someone must see to properly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">家畜の餌に、肥料、研磨剤、耐火ブランケット、魔法書代と。
+修繕費は、訓練木人が二体、鍋、三つ。フライパン、二つ、ジョウロ…四つ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livestock feed, fertilizer, polishing powders, fireproof blankets, spellbook expenses...
+And for repairs, let's see: two training dummies, three cooking pots, two frying pans, and... four watering cans?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…四つ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Four?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…犯人は明白だな。備品損耗、と。うむ、これでいい。
+ついでにコルゴンの食費も…必要……経費……と……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...The culprit is obvious. "Equipment wear and tear," then. Hmm, that will do.
+And Corgon's food expenses while I'm at it... a... necessary... expenditure...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うーん…眠い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mmm... I'm getting sleepy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（むにゅ…むにゃ…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Mnh... mngh...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（すや…すや…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Zzz... zzz...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…さん…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sir...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ロイテル…さん…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sir Loytel...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（すや…すや…ぅう……）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Zzz... zzz... nnh......)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…やれるよ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...I can make it...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん…ボクはまだやれるよ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel... I can still make it...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん、私たちを見捨てないで…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel...Don't abandon us...!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（う…ウウウ…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Nn... Nnngh...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pebble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボクたちを使って…ボクたちはまだやれるよ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use us... We can still make it!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん、私たちを輝かせて！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel, make us shine!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ウウウ…！）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Nnngh...!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ハッ…！）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Haah...!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はぁ…はぁ…私としたことが、仕事中に眠ってしまったのか。
+それにしても、妙にリアルな夢だった。まるで、石ころが本当に耳元で囁いているかのような…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haah... haah... To think that I would fall asleep in the middle of my work.
+Even so, that dream felt strangely real. It was almost as though the pebbles themselves were truly whispering into my ear...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お疲れのようですね、ロイテル様。うたた寝なさっていたのですか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You seem tired, Lord Loytel. Were you taking a little nap?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスさん…あなたは、そこで何を…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lady Farris... What were you doing there...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何も。ただ、小石たちの切なる声に耳を傾けていただけです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing at all. I was merely listening to the earnest voices of the pebbles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…小石は喋りません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But pebbles do not speak...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">では、夢だったのでしょう…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Then it must have been a dream...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（夢…だったのかな…？）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A dream... was it...?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reward_stone_dream</t>
+  </si>
 </sst>
 </file>
 
@@ -3818,7 +4017,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3929,6 +4128,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック;Noto Sans JP;游ゴシック;メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3978,7 +4184,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4101,6 +4307,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4301,7 +4511,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N709"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
@@ -4357,7 +4567,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="1" t="n">
         <f aca="false">MAX(I4:I1048576)</f>
-        <v>425</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11752,8 +11962,593 @@
         <v>98</v>
       </c>
     </row>
+    <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A711" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="F711" s="1"/>
+    </row>
+    <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D712" s="4"/>
+      <c r="E712" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F712" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="G712" s="4"/>
+    </row>
+    <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D713" s="4"/>
+      <c r="E713" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F713" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="G713" s="4"/>
+    </row>
+    <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D714" s="4"/>
+      <c r="E714" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="F714" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G714" s="4"/>
+    </row>
+    <row r="715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D715" s="4"/>
+      <c r="E715" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F715" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="G715" s="4"/>
+    </row>
+    <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D716" s="4"/>
+      <c r="E716" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F716" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="G716" s="4"/>
+    </row>
+    <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D717" s="4"/>
+      <c r="E717" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F717" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G717" s="4"/>
+    </row>
+    <row r="718" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F718" s="1"/>
+      <c r="J718" s="12"/>
+      <c r="K718" s="30"/>
+    </row>
+    <row r="719" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F719" s="1"/>
+      <c r="I719" s="6" t="n">
+        <v>426</v>
+      </c>
+      <c r="J719" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="K719" s="8" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="720" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F720" s="1"/>
+      <c r="I720" s="6" t="n">
+        <v>427</v>
+      </c>
+      <c r="J720" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="K720" s="8" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="721" customFormat="false" ht="49.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F721" s="1"/>
+      <c r="I721" s="6" t="n">
+        <v>428</v>
+      </c>
+      <c r="J721" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="K721" s="31" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F722" s="1"/>
+      <c r="I722" s="6" t="n">
+        <v>429</v>
+      </c>
+      <c r="J722" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="K722" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="723" customFormat="false" ht="49.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F723" s="1"/>
+      <c r="I723" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="J723" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="K723" s="31" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F724" s="1"/>
+      <c r="I724" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="J724" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="K724" s="31" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F725" s="1"/>
+      <c r="I725" s="6" t="n">
+        <v>432</v>
+      </c>
+      <c r="J725" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="K725" s="31" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A726" s="4"/>
+      <c r="B726" s="4"/>
+      <c r="C726" s="4"/>
+      <c r="D726" s="4"/>
+      <c r="F726" s="1"/>
+      <c r="G726" s="4"/>
+      <c r="H726" s="4"/>
+      <c r="I726" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="J726" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="K726" s="31" t="s">
+        <v>831</v>
+      </c>
+      <c r="L726" s="4"/>
+      <c r="M726" s="1"/>
+      <c r="N726" s="1"/>
+    </row>
+    <row r="727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D727" s="4"/>
+      <c r="E727" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="F727" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G727" s="4"/>
+    </row>
+    <row r="728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D728" s="4"/>
+      <c r="E728" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F728" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G728" s="4"/>
+    </row>
+    <row r="729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D729" s="4"/>
+      <c r="E729" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F729" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="G729" s="4"/>
+    </row>
+    <row r="730" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A730" s="4"/>
+      <c r="B730" s="4"/>
+      <c r="C730" s="4"/>
+      <c r="D730" s="4"/>
+      <c r="F730" s="1"/>
+      <c r="G730" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="H730" s="4"/>
+      <c r="I730" s="6" t="n">
+        <v>434</v>
+      </c>
+      <c r="J730" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K730" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L730" s="4"/>
+      <c r="M730" s="1"/>
+      <c r="N730" s="1"/>
+    </row>
+    <row r="731" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F731" s="1"/>
+      <c r="G731" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I731" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="J731" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="K731" s="4" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="732" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E732" s="4"/>
+      <c r="F732" s="16"/>
+      <c r="G732" s="26" t="s">
+        <v>832</v>
+      </c>
+      <c r="I732" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="J732" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="K732" s="8" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F733" s="1"/>
+      <c r="G733" s="4"/>
+      <c r="I733" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="J733" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="K733" s="31" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="734" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F734" s="1"/>
+      <c r="G734" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I734" s="6" t="n">
+        <v>438</v>
+      </c>
+      <c r="J734" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="K734" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="735" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F735" s="1"/>
+      <c r="G735" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I735" s="6" t="n">
+        <v>439</v>
+      </c>
+      <c r="J735" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="K735" s="31" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="736" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D736" s="4"/>
+      <c r="E736" s="4"/>
+      <c r="F736" s="1"/>
+      <c r="G736" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I736" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="J736" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="K736" s="8" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="737" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F737" s="1"/>
+      <c r="G737" s="4"/>
+      <c r="I737" s="6" t="n">
+        <v>441</v>
+      </c>
+      <c r="J737" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="K737" s="31" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F738" s="1"/>
+      <c r="G738" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="I738" s="6" t="n">
+        <v>442</v>
+      </c>
+      <c r="J738" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="K738" s="31" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="739" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F739" s="1"/>
+      <c r="G739" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="I739" s="6" t="n">
+        <v>443</v>
+      </c>
+      <c r="J739" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="K739" s="31" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E740" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F740" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I740" s="6"/>
+      <c r="J740" s="12"/>
+      <c r="K740" s="8"/>
+    </row>
+    <row r="741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F741" s="1"/>
+      <c r="G741" s="4"/>
+      <c r="I741" s="6" t="n">
+        <v>444</v>
+      </c>
+      <c r="J741" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="K741" s="31" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="742" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F742" s="1"/>
+      <c r="I742" s="6" t="n">
+        <v>445</v>
+      </c>
+      <c r="J742" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="K742" s="31" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E743" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F743" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I743" s="6"/>
+      <c r="J743" s="12"/>
+      <c r="K743" s="8"/>
+    </row>
+    <row r="744" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F744" s="1"/>
+      <c r="G744" s="4"/>
+      <c r="I744" s="6" t="n">
+        <v>446</v>
+      </c>
+      <c r="J744" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="K744" s="31" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="745" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F745" s="1"/>
+      <c r="G745" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I745" s="6" t="n">
+        <v>447</v>
+      </c>
+      <c r="J745" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K745" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="746" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F746" s="1"/>
+      <c r="G746" s="4"/>
+      <c r="I746" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="J746" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K746" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F747" s="1"/>
+      <c r="G747" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I747" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="J747" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="K747" s="31" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="748" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F748" s="1"/>
+      <c r="G748" s="4"/>
+      <c r="I748" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="J748" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="K748" s="8" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="749" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F749" s="1"/>
+      <c r="G749" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I749" s="6" t="n">
+        <v>451</v>
+      </c>
+      <c r="J749" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="K749" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F750" s="1"/>
+      <c r="G750" s="4"/>
+      <c r="I750" s="6" t="n">
+        <v>452</v>
+      </c>
+      <c r="J750" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="K750" s="31" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="751" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F751" s="1"/>
+      <c r="G751" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I751" s="6" t="n">
+        <v>453</v>
+      </c>
+      <c r="J751" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="K751" s="31" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F752" s="1"/>
+      <c r="G752" s="4"/>
+      <c r="I752" s="6" t="n">
+        <v>454</v>
+      </c>
+      <c r="J752" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K752" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F753" s="1"/>
+      <c r="G753" s="4"/>
+      <c r="I753" s="6" t="n">
+        <v>455</v>
+      </c>
+      <c r="J753" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="K753" s="31" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F754" s="1"/>
+      <c r="G754" s="4"/>
+      <c r="I754" s="6"/>
+      <c r="J754" s="6"/>
+      <c r="K754" s="8"/>
+    </row>
+    <row r="755" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E755" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F755" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J755" s="6"/>
+      <c r="K755" s="6"/>
+    </row>
+    <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E756" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F756" s="1"/>
+    </row>
+    <row r="757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E757" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F757" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E758" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F758" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I108:I339 I4:I106 J656 J615:J619 J650:J651 J623 J637 I658:I1048576 I611:I614 I341:I553 J547:J550 I599:I601 J599 I597:J598 I616:I656">
+  <conditionalFormatting sqref="I108:I339 I4:I106 J656 J615:J619 J650:J651 J623 J637 I611:I614 I341:I553 J547:J550 I599:I601 J599 I597:J598 I616:I656 J712:J715 J730:J754 I658:I1048576 J719:J727">
     <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I602:I610 I564:I596 I554:I561">
